--- a/public/templates/QRP-yeni.xlsx
+++ b/public/templates/QRP-yeni.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$G$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$G$38</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -91,12 +91,6 @@
     <t xml:space="preserve">Aşağıda qeyd olunan malların göndərilməsi haqqında çərçivə müqaviləsinin şərtlərinin əsasında sifariş olunmuşdur. </t>
   </si>
   <si>
-    <t>Qiymət razılaşma pratokulu №366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"AzRosPromİnvest” Məhdud Məsuliyyət  Cəmiyyəti                                                     </t>
-  </si>
-  <si>
     <t>Şayba M24 (yaylı)</t>
   </si>
   <si>
@@ -107,6 +101,12 @@
   </si>
   <si>
     <t>Qayka M24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"ASG Business Aviation” Məhdud Məsuliyyət  Cəmiyyəti                                                     </t>
+  </si>
+  <si>
+    <t>T№411</t>
   </si>
 </sst>
 </file>
@@ -178,7 +178,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -214,11 +214,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -227,12 +253,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -243,35 +263,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -346,15 +390,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>146050</xdr:rowOff>
+      <xdr:colOff>387350</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>240665</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:colOff>247015</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -377,7 +421,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3937000" y="5949950"/>
+          <a:off x="3359150" y="5461000"/>
           <a:ext cx="1523365" cy="1524000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -397,13 +441,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>31750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>339725</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>135255</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -709,10 +753,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.6328125" customWidth="1"/>
+    <col min="1" max="1" width="6.453125" customWidth="1"/>
     <col min="2" max="2" width="12.7265625" customWidth="1"/>
     <col min="3" max="3" width="10.6328125" customWidth="1"/>
     <col min="4" max="4" width="12.7265625" customWidth="1"/>
@@ -722,210 +766,210 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="9"/>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="A1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
     </row>
     <row r="9" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="10"/>
+      <c r="B9" s="18"/>
       <c r="C9" s="1"/>
-      <c r="G9" s="18">
-        <v>46250</v>
+      <c r="G9" s="10">
+        <v>46269</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
+      <c r="B11" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
     </row>
     <row r="16" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="5" t="s">
+      <c r="C16" s="24"/>
+      <c r="D16" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="4">
+      <c r="A17" s="9">
         <v>1</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="26"/>
+      <c r="D17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="11">
+        <v>1.3</v>
+      </c>
+      <c r="F17" s="11">
+        <v>5</v>
+      </c>
+      <c r="G17" s="11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="9">
+        <v>2</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="26"/>
+      <c r="D18" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="11">
+        <v>1.7</v>
+      </c>
+      <c r="F18" s="11">
+        <v>5</v>
+      </c>
+      <c r="G18" s="11">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="9">
+        <v>3</v>
+      </c>
+      <c r="B19" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="4" t="s">
+      <c r="C19" s="26"/>
+      <c r="D19" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="19">
-        <v>1.3</v>
-      </c>
-      <c r="F17" s="19">
+      <c r="E19" s="11">
+        <v>20</v>
+      </c>
+      <c r="F19" s="11">
+        <v>8</v>
+      </c>
+      <c r="G19" s="11">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="9">
+        <v>4</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="26"/>
+      <c r="D20" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="11">
         <v>5</v>
       </c>
-      <c r="G17" s="19">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="4">
-        <v>2</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="19">
-        <v>1.7</v>
-      </c>
-      <c r="F18" s="19">
-        <v>5</v>
-      </c>
-      <c r="G18" s="19">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="4">
-        <v>3</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="19">
-        <v>20</v>
-      </c>
-      <c r="F19" s="19">
+      <c r="F20" s="11">
         <v>8</v>
       </c>
-      <c r="G19" s="19">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="4">
-        <v>4</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="19">
-        <v>5</v>
-      </c>
-      <c r="F20" s="19">
-        <v>8</v>
-      </c>
-      <c r="G20" s="19">
+      <c r="G20" s="11">
         <v>40</v>
       </c>
     </row>
@@ -934,10 +978,10 @@
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="E21" s="3"/>
-      <c r="F21" s="20" t="s">
+      <c r="F21" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="11">
         <v>215</v>
       </c>
     </row>
@@ -946,10 +990,10 @@
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="11">
         <v>38.700000000000003</v>
       </c>
     </row>
@@ -958,168 +1002,157 @@
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="11">
         <v>253.7</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-    </row>
-    <row r="29" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="14" t="s">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="22"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="14" t="s">
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+    </row>
+    <row r="26" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" s="15"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="16"/>
+      <c r="A31" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="16" t="s">
+        <v>14</v>
+      </c>
       <c r="F31" s="16"/>
       <c r="G31" s="16"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
+      <c r="A34" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="17"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="A30:C31"/>
-    <mergeCell ref="E30:G31"/>
-    <mergeCell ref="A35:C36"/>
-    <mergeCell ref="E35:G36"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
@@ -1129,6 +1162,12 @@
     <mergeCell ref="A13:G14"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="A26:C27"/>
+    <mergeCell ref="E26:G27"/>
+    <mergeCell ref="A31:C32"/>
+    <mergeCell ref="E31:G32"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.2" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
